--- a/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
+++ b/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B44090-BC47-4F5A-8B8D-9706BFC75B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174F4028-4450-46F2-8208-437DB69288B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
   <si>
     <t>TOTAL</t>
   </si>
@@ -380,9 +380,6 @@
     <t>Christian / Vanina</t>
   </si>
   <si>
-    <t>Subidos en ABR 2025</t>
-  </si>
-  <si>
     <t>CAJA ANTERIOR</t>
   </si>
   <si>
@@ -410,15 +407,9 @@
     <t>Seguro de consorcio obligatorio -  federacion patronal - poliza nro. 2027630</t>
   </si>
   <si>
-    <t>SAC</t>
-  </si>
-  <si>
     <t>Anabella</t>
   </si>
   <si>
-    <t>ARBA</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
@@ -432,6 +423,12 @@
   </si>
   <si>
     <t>EGRESOS DEL MES DE JULIO</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Provision y colocacion de Coliza</t>
+  </si>
+  <si>
+    <t>Subidos en JULI 2025</t>
   </si>
 </sst>
 </file>
@@ -439,19 +436,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="13">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -668,6 +665,7 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1125,11 +1123,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1137,7 +1135,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1146,27 +1144,27 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1179,8 +1177,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1188,16 +1186,16 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1208,8 +1206,8 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1228,7 +1226,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1239,28 +1237,28 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1275,13 +1273,13 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1292,24 +1290,24 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1319,7 +1317,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,19 +1332,19 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1355,7 +1353,7 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1365,37 +1363,37 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1405,10 +1403,10 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1417,8 +1415,8 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1427,9 +1425,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1437,11 +1435,11 @@
     <xf numFmtId="43" fontId="26" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1449,10 +1447,10 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1460,12 +1458,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="174" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="171" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1476,13 +1470,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1493,9 +1487,10 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1908,17 +1903,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1926,452 +1921,432 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="220">
+      <c r="C18" s="218">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="221">
+      <c r="C19" s="219">
         <v>350140.35</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="218">
-        <v>197132.7</v>
+      <c r="C20" s="219">
+        <v>280000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>26</v>
+      </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="221">
-        <v>280000</v>
+      <c r="C21" s="218">
+        <v>65000</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="220">
-        <v>65000</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B22" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="33">
-        <v>78682.460000000006</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="6"/>
-      <c r="F23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="23">
-        <f>SUM(C17:C23)</f>
-        <v>1047609.51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+      <c r="C22" s="218">
+        <v>83400</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6"/>
+      <c r="F22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="23">
+        <f>SUM(C17:C22)</f>
+        <v>855194.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="214"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="39"/>
+      <c r="C24" s="214"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="218">
+        <f>349151.87+ (349151.87*10%)</f>
+        <v>384067.05699999997</v>
+      </c>
+      <c r="D25" s="45"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="33">
-        <v>349151.87</v>
+      <c r="C26" s="218">
+        <v>5684</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="210" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="33">
-        <f>C26/2</f>
-        <v>174575.935</v>
+      <c r="B27" s="140"/>
+      <c r="C27" s="218">
+        <v>52800</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="220">
-        <v>5684</v>
-      </c>
-      <c r="D28" s="45"/>
+      <c r="C28" s="218">
+        <v>45000</v>
+      </c>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="210" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" s="140"/>
-      <c r="C29" s="220">
-        <v>52800</v>
-      </c>
-      <c r="D29" s="45"/>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="220">
-        <v>45000</v>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="40"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="23">
+        <f>SUM(C24:C29)</f>
+        <v>487551.05699999997</v>
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6"/>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30"/>
+      <c r="C31" s="43">
+        <f>+C30+C23</f>
+        <v>1342745.4069999999</v>
+      </c>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="23">
-        <f>SUM(C25:C31)</f>
-        <v>627211.80499999993</v>
-      </c>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C32" s="24"/>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="43">
-        <f>+C32+C24</f>
-        <v>1674821.3149999999</v>
-      </c>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C34" s="24"/>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="33"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="24"/>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="34"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
-      <c r="C36" s="33"/>
+      <c r="C36" s="34"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="34"/>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C37" s="25"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="215" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="215"/>
+      <c r="C38" s="216">
+        <v>1000000</v>
+      </c>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" s="215"/>
-      <c r="C40" s="216">
-        <v>1000000</v>
-      </c>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C41" s="25"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14">
-        <f>+C36+C37+C38+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+      <c r="B40" s="13"/>
+      <c r="C40" s="14">
+        <f>+C34+C35+C36+C39</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19">
-        <f>+C42+C33</f>
-        <v>1674821.3149999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19">
+        <f>+C40+C31</f>
+        <v>1342745.4069999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="C45" s="162"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="C47" s="162"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="4"/>
-      <c r="C48" s="162"/>
+      <c r="C46" s="162"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="163" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="161"/>
+      <c r="C47" s="164">
+        <v>-135380.74219829985</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="163" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="161"/>
+      <c r="C48" s="166">
+        <f>-(C31-C29)</f>
+        <v>-1342745.4069999999</v>
+      </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="163" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B49" s="161"/>
-      <c r="C49" s="164">
-        <v>-572529.8020046202</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="163" t="s">
-        <v>134</v>
-      </c>
-      <c r="B50" s="161"/>
-      <c r="C50" s="166">
-        <f>-(C33-C31)</f>
-        <v>-1674821.3149999999</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="163" t="s">
-        <v>113</v>
-      </c>
-      <c r="B51" s="161"/>
-      <c r="C51" s="208">
+      <c r="C49" s="208">
         <f>'prorrateo '!F31</f>
         <v>2012565.1348063203</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="167"/>
-      <c r="C52" s="168"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="165" t="s">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="167"/>
+      <c r="C50" s="168"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="160"/>
-      <c r="C53" s="169">
-        <f>SUM(C47:C51)</f>
-        <v>-234785.98219829961</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="222"/>
-      <c r="B55" s="222"/>
-      <c r="C55" s="222"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="223"/>
-      <c r="B56" s="223"/>
-      <c r="C56" s="223"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="B51" s="160"/>
+      <c r="C51" s="169">
+        <f>SUM(C45:C49)</f>
+        <v>534438.98560802056</v>
+      </c>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="10"/>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="220"/>
+      <c r="B53" s="220"/>
+      <c r="C53" s="220"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="221"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="221"/>
+    </row>
+    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28" t="s">
+      <c r="B55" s="27"/>
+      <c r="C55" s="29"/>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
         <v>24</v>
       </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="31">
+        <f>-C40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="31"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="31">
-        <f>-C42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="31"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="32"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="171"/>
-      <c r="C61" s="172">
-        <f>SUM(C57:C60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C58" s="32"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="171"/>
+      <c r="C59" s="172">
+        <f>SUM(C55:C58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A55:C56"/>
+    <mergeCell ref="A53:C54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2389,45 +2364,45 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="224">
+        <v>121</v>
+      </c>
+      <c r="B1" s="222">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="224"/>
+      <c r="C1" s="222"/>
       <c r="D1" s="144">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="226">
+        <v>120</v>
+      </c>
+      <c r="G1" s="224">
         <v>1000000</v>
       </c>
-      <c r="H1" s="226"/>
-    </row>
-    <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="224"/>
+    </row>
+    <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>27</v>
       </c>
@@ -2453,10 +2428,10 @@
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="50" t="s">
         <v>123</v>
-      </c>
-      <c r="J2" s="50" t="s">
-        <v>124</v>
       </c>
       <c r="K2" s="50" t="s">
         <v>17</v>
@@ -2465,7 +2440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>32</v>
       </c>
@@ -2507,12 +2482,12 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>35</v>
@@ -2549,7 +2524,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
@@ -2588,7 +2563,7 @@
         <v>328762.85139613436</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>39</v>
       </c>
@@ -2628,7 +2603,7 @@
         <v>181107.19149100001</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>36</v>
       </c>
@@ -2670,7 +2645,7 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>42</v>
       </c>
@@ -2710,7 +2685,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2725,7 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="213" t="s">
         <v>46</v>
       </c>
@@ -2789,7 +2764,7 @@
         <v>621121.39307699248</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>112</v>
       </c>
@@ -2829,7 +2804,7 @@
         <v>122781.74378399999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>49</v>
       </c>
@@ -2869,7 +2844,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>51</v>
       </c>
@@ -2911,12 +2886,12 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="141" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C14" s="65" t="s">
         <v>54</v>
@@ -2953,7 +2928,7 @@
         <v>240823.6387943312</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>55</v>
       </c>
@@ -2992,7 +2967,7 @@
         <v>250474.75731935998</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>58</v>
       </c>
@@ -3034,7 +3009,7 @@
         <v>181107.19149100001</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>61</v>
       </c>
@@ -3074,7 +3049,7 @@
         <v>122781.74378399999</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62" t="s">
         <v>63</v>
       </c>
@@ -3114,7 +3089,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>65</v>
       </c>
@@ -3154,7 +3129,7 @@
         <v>180274.78253999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="187"/>
       <c r="B20" s="188" t="s">
         <v>116</v>
@@ -3193,7 +3168,7 @@
         <v>131790.00088863494</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="59" t="s">
         <v>59</v>
@@ -3233,7 +3208,7 @@
         <v>37542.373668</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="145"/>
       <c r="B22" s="146"/>
       <c r="C22" s="147" t="s">
@@ -3270,7 +3245,7 @@
         <v>131790.00088863494</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
         <v>37</v>
@@ -3307,7 +3282,7 @@
         <v>70449.182442028789</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>51</v>
       </c>
@@ -3349,7 +3324,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -3389,7 +3364,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>65</v>
       </c>
@@ -3429,7 +3404,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>65</v>
       </c>
@@ -3473,7 +3448,7 @@
         <v>232895.52987599999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
       <c r="B28" s="67" t="str">
         <f>B7</f>
@@ -3514,7 +3489,7 @@
         <v>26310.373668</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
         <v>55</v>
       </c>
@@ -3553,7 +3528,7 @@
         <v>53673.162282719997</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
       <c r="C30" s="70"/>
@@ -3567,7 +3542,7 @@
       <c r="K30" s="73"/>
       <c r="L30" s="73"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="74"/>
       <c r="B31" s="75"/>
       <c r="C31" s="76" t="s">
@@ -3598,68 +3573,68 @@
         <v>3785826.0815708381</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="225"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
-      <c r="G33" s="225"/>
-      <c r="H33" s="225"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
-      <c r="L33" s="225"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="225"/>
-      <c r="B34" s="225"/>
-      <c r="C34" s="225"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="225"/>
-      <c r="B35" s="225"/>
-      <c r="C35" s="225"/>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="225"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="225"/>
-      <c r="B36" s="225"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="225"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
-      <c r="L36" s="225"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="223" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="223"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="223"/>
+      <c r="J33" s="223"/>
+      <c r="K33" s="223"/>
+      <c r="L33" s="223"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="223"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="223"/>
+      <c r="J34" s="223"/>
+      <c r="K34" s="223"/>
+      <c r="L34" s="223"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="223"/>
+      <c r="B35" s="223"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="223"/>
+      <c r="K35" s="223"/>
+      <c r="L35" s="223"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="223"/>
+      <c r="B36" s="223"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="223"/>
+      <c r="J36" s="223"/>
+      <c r="K36" s="223"/>
+      <c r="L36" s="223"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3677,45 +3652,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="227" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="225" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="228"/>
-      <c r="F1" s="228"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="229"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="227"/>
       <c r="O1" s="78"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="176"/>
@@ -3733,7 +3708,7 @@
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="178"/>
@@ -3751,7 +3726,7 @@
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
       <c r="C4" s="178"/>
@@ -3771,7 +3746,7 @@
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
       <c r="C5" s="178"/>
@@ -3789,7 +3764,7 @@
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
       <c r="C6" s="176"/>
@@ -3807,13 +3782,13 @@
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="83"/>
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="219">
-        <v>510646.76</v>
+      <c r="C7" s="230">
+        <v>662901.94999999995</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="176"/>
@@ -3834,7 +3809,7 @@
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="83"/>
       <c r="B8" s="82" t="s">
         <v>79</v>
@@ -3850,16 +3825,16 @@
         <f>C8-J38</f>
         <v>-227016.12285000001</v>
       </c>
-      <c r="L8" s="231">
+      <c r="L8" s="229">
         <f>C7-J38</f>
-        <v>283630.63714999997</v>
-      </c>
-      <c r="M8" s="231"/>
+        <v>435885.82714999991</v>
+      </c>
+      <c r="M8" s="229"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="89" t="s">
         <v>80</v>
       </c>
@@ -3904,7 +3879,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="100">
         <v>1</v>
       </c>
@@ -3944,7 +3919,7 @@
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>14493.525558365</v>
+        <v>22273.765767364996</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
@@ -3952,15 +3927,15 @@
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>45002.436658365019</v>
+        <v>52782.676867365015</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>169489.48243936503</v>
+        <v>177269.72264836502</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="101">
         <v>2</v>
       </c>
@@ -4000,7 +3975,7 @@
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>14436.799430934998</v>
+        <v>22186.588601934993</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -4008,15 +3983,15 @@
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>33419.28823093501</v>
+        <v>41169.077401935006</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>157419.10486993502</v>
+        <v>165168.894040935</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="100">
         <v>3</v>
       </c>
@@ -4056,7 +4031,7 @@
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>14294.984112359998</v>
+        <v>21968.645688359993</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
@@ -4064,18 +4039,18 @@
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>19153.150712359995</v>
+        <v>26826.81228835999</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>347916.00210849434</v>
+        <v>355589.66368449433</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="100">
         <v>4</v>
       </c>
@@ -4115,7 +4090,7 @@
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>14777.156195514999</v>
+        <v>22709.651594514995</v>
       </c>
       <c r="M13" s="183">
         <f t="shared" si="4"/>
@@ -4123,15 +4098,15 @@
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>23377.424095515002</v>
+        <v>31309.919494515001</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>204484.61558651499</v>
+        <v>212417.110985515</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="100">
         <v>6</v>
       </c>
@@ -4171,7 +4146,7 @@
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>14493.525558365</v>
+        <v>22273.765767364996</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
@@ -4179,15 +4154,15 @@
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>21405.627458365005</v>
+        <v>29185.867667365001</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>145892.67323936502</v>
+        <v>153672.913448365</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="100">
         <v>7</v>
       </c>
@@ -4227,7 +4202,7 @@
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>14436.799430934998</v>
+        <v>22186.588601934993</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
@@ -4235,14 +4210,14 @@
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>29742.837830934979</v>
+        <v>37492.627001934976</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>153742.65446993499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>161492.44364093497</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="100">
         <v>8</v>
       </c>
@@ -4282,7 +4257,7 @@
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>14493.525558365</v>
+        <v>22273.765767364996</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
@@ -4290,14 +4265,14 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>24078.556958364985</v>
+        <v>31858.797167364981</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>148565.60273936499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>156345.842948365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="100">
         <v>9</v>
       </c>
@@ -4337,7 +4312,7 @@
       </c>
       <c r="L17" s="203">
         <f t="shared" si="3"/>
-        <v>14436.799430934998</v>
+        <v>22186.588601934993</v>
       </c>
       <c r="M17" s="204">
         <f t="shared" si="4"/>
@@ -4345,14 +4320,14 @@
       </c>
       <c r="N17" s="199">
         <f t="shared" si="5"/>
-        <v>25175.410930934999</v>
+        <v>32925.200101934992</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>646296.80400792742</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>654046.59317892743</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="100">
         <v>10</v>
       </c>
@@ -4392,7 +4367,7 @@
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>14294.984112359998</v>
+        <v>21968.645688359993</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
@@ -4400,14 +4375,14 @@
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>23504.867512360004</v>
+        <v>31178.529088359996</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>146286.61129636</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>153960.27287235999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="100">
         <v>11</v>
       </c>
@@ -4447,7 +4422,7 @@
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>14777.156195514999</v>
+        <v>22709.651594514995</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
@@ -4455,14 +4430,14 @@
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>37023.432595515027</v>
+        <v>44955.927994515019</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>163946.62408651505</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>171879.11948551502</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="100">
         <v>12</v>
       </c>
@@ -4502,7 +4477,7 @@
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>14493.525558365</v>
+        <v>22273.765767364996</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
@@ -4510,14 +4485,14 @@
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>36721.044558365</v>
+        <v>44501.284767364996</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>161208.09033936501</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>168988.33054836502</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="100">
         <v>13</v>
       </c>
@@ -4557,7 +4532,7 @@
       </c>
       <c r="L21" s="129">
         <f t="shared" si="3"/>
-        <v>14436.799430934998</v>
+        <v>22186.588601934993</v>
       </c>
       <c r="M21" s="109">
         <f t="shared" si="4"/>
@@ -4565,14 +4540,14 @@
       </c>
       <c r="N21" s="106">
         <f t="shared" si="5"/>
-        <v>14493.07163093499</v>
+        <v>22242.860801934985</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>255316.71042526618</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>263066.49959626619</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="100">
         <v>14</v>
       </c>
@@ -4612,7 +4587,7 @@
       </c>
       <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>14294.984112359998</v>
+        <v>21968.645688359993</v>
       </c>
       <c r="M22" s="109">
         <f t="shared" si="4"/>
@@ -4620,14 +4595,14 @@
       </c>
       <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>23687.752162360008</v>
+        <v>31361.413738360003</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>274162.50948171999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>281836.17105771997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="100">
         <v>15</v>
       </c>
@@ -4667,7 +4642,7 @@
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>14777.156195514999</v>
+        <v>22709.651594514995</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
@@ -4675,14 +4650,14 @@
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>27513.430795515014</v>
+        <v>35445.926194515014</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>208620.62228651502</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>216553.11768551503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="100">
         <v>16</v>
       </c>
@@ -4722,7 +4697,7 @@
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>14294.984112359998</v>
+        <v>21968.645688359993</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
@@ -4730,14 +4705,14 @@
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>17474.363412360006</v>
+        <v>25148.024988360001</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>140256.10719636001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>147929.76877236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="100">
         <v>17</v>
       </c>
@@ -4777,7 +4752,7 @@
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>14777.156195514999</v>
+        <v>22709.651594514995</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
@@ -4785,14 +4760,14 @@
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>21848.695995515009</v>
+        <v>29781.191394515005</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>148771.88748651501</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>156704.38288551502</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="100">
         <v>18</v>
       </c>
@@ -4832,7 +4807,7 @@
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>20988.667149099998</v>
+        <v>32255.551209099995</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
@@ -4840,14 +4815,14 @@
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>56393.2596491</v>
+        <v>67660.143709099997</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>236668.0421891</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>247934.92624909998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="100">
         <v>19</v>
       </c>
@@ -4877,21 +4852,21 @@
       <c r="K27" s="202"/>
       <c r="L27" s="203">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M27" s="204">
         <v>0</v>
       </c>
       <c r="N27" s="199">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>134853.21176985494</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>136497.56782185493</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="100">
         <v>20</v>
       </c>
@@ -4916,21 +4891,21 @@
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>40605.584549220002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>42249.940601219998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
       <c r="C29" s="173" t="s">
@@ -4948,21 +4923,21 @@
       <c r="K29" s="154"/>
       <c r="L29" s="155">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M29" s="156">
         <v>0</v>
       </c>
       <c r="N29" s="153">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>134853.21176985494</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>136497.56782185493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
       <c r="C30" s="184" t="s">
@@ -4980,21 +4955,21 @@
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>73512.393323248791</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>75156.749375248794</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
       <c r="C31" s="184" t="s">
@@ -5012,21 +4987,21 @@
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>29373.584549219999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31017.940601219998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="100"/>
       <c r="B32" s="92"/>
       <c r="C32" s="132" t="s">
@@ -5044,21 +5019,21 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>29373.584549219999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31017.940601219998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="100"/>
       <c r="B33" s="92"/>
       <c r="C33" s="132" t="s">
@@ -5076,21 +5051,21 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>29373.584549219999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31017.940601219998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="100"/>
       <c r="B34" s="92"/>
       <c r="C34" s="132" t="s">
@@ -5108,21 +5083,21 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>29373.584549219999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31017.940601219998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="100">
         <v>21</v>
       </c>
@@ -5147,21 +5122,21 @@
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>29373.584549219999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31017.940601219998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="100">
         <v>22</v>
       </c>
@@ -5186,21 +5161,21 @@
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="M36" s="109">
         <v>0</v>
       </c>
       <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>3063.2108812199999</v>
+        <v>4707.5669332199996</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>56736.373163939999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58380.729215939995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="100">
         <v>23</v>
       </c>
@@ -5230,7 +5205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="100">
         <v>24</v>
       </c>
@@ -5249,16 +5224,16 @@
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>283630.63715000002</v>
+        <v>435885.82715000008</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>510646.76000000013</v>
+        <v>662901.95000000007</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="80"/>
       <c r="C39" s="93"/>
       <c r="D39" s="94"/>
@@ -5277,47 +5252,47 @@
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>510646.76</v>
+        <v>662901.95000000007</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
       <c r="O39" s="81"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="230"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
-      <c r="G40" s="228"/>
-      <c r="H40" s="228"/>
-      <c r="I40" s="228"/>
-      <c r="J40" s="228"/>
-      <c r="K40" s="228"/>
-      <c r="L40" s="228"/>
-      <c r="M40" s="228"/>
-      <c r="N40" s="228"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="226"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="226"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="226"/>
       <c r="O40" s="97"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="81"/>
       <c r="J41" s="98"/>
       <c r="K41" s="98"/>
       <c r="L41" s="98"/>
       <c r="N41" s="99"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="157"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="158"/>
       <c r="F46" s="158"/>
       <c r="G46" s="158"/>

--- a/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
+++ b/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174F4028-4450-46F2-8208-437DB69288B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1318F77-F975-4AAA-A958-C39B5485B956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="137">
   <si>
     <t>TOTAL</t>
   </si>
@@ -401,9 +401,6 @@
     <t>EXTRAORDINARIAS</t>
   </si>
   <si>
-    <t>El 4B abonó parte de la deuda que tiene hasta Octubre de 2024 con la constructora, entendiendo que este mes cancela el resto</t>
-  </si>
-  <si>
     <t>Seguro de consorcio obligatorio -  federacion patronal - poliza nro. 2027630</t>
   </si>
   <si>
@@ -429,6 +426,18 @@
   </si>
   <si>
     <t>Subidos en JULI 2025</t>
+  </si>
+  <si>
+    <t>TSG MES 4</t>
+  </si>
+  <si>
+    <t>TSG MES 5</t>
+  </si>
+  <si>
+    <t>TSG MES 6</t>
+  </si>
+  <si>
+    <t>TSG MES 7</t>
   </si>
 </sst>
 </file>
@@ -450,7 +459,7 @@
     <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,6 +677,12 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1127,7 +1142,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1349,11 +1364,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1460,10 +1470,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1490,7 +1497,13 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1903,7 +1916,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F63"/>
+  <dimension ref="A2:F67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1941,10 +1954,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1993,10 +2006,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="218">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
@@ -2007,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="219">
+      <c r="C19" s="228">
         <v>350140.35</v>
       </c>
       <c r="D19" s="20"/>
@@ -2015,10 +2028,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="219">
+      <c r="C20" s="228">
         <v>280000</v>
       </c>
       <c r="D20" s="20"/>
@@ -2029,7 +2042,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="218">
+      <c r="C21" s="33">
         <v>65000</v>
       </c>
       <c r="D21" s="20"/>
@@ -2037,317 +2050,362 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="33">
+        <v>15181</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="33">
+        <v>15181</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="33">
+        <v>14134</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="33">
+        <v>14856</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B26" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="218">
+      <c r="C26" s="33">
         <v>83400</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="6"/>
-      <c r="F22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="23">
-        <f>SUM(C17:C22)</f>
-        <v>855194.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="6"/>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="40"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="23">
+        <f>SUM(C17:C26)</f>
+        <v>914546.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="214"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="B28" s="39"/>
+      <c r="C28" s="211"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="218">
+      <c r="B29" s="42"/>
+      <c r="C29" s="33">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="D29" s="45"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="218">
+      <c r="B30" s="42"/>
+      <c r="C30" s="33">
         <v>5684</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="210" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="140"/>
-      <c r="C27" s="218">
+      <c r="D30" s="45"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="207" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="140"/>
+      <c r="C31" s="33">
         <v>52800</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="D31" s="45"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="42"/>
+      <c r="C32" s="33">
+        <v>45000</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="23">
+        <f>SUM(C28:C33)</f>
+        <v>487551.05699999997</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="43">
+        <f>+C34+C27</f>
+        <v>1402097.4069999999</v>
+      </c>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="24"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="33"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="34"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="34"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C41" s="25"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="212" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="212"/>
+      <c r="C42" s="213">
+        <v>1000000</v>
+      </c>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C43" s="25"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14">
+        <f>+C38+C39+C40+C43</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19">
+        <f>+C44+C35</f>
+        <v>1402097.4069999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="C49" s="159"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="C50" s="159"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="160" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="158"/>
+      <c r="C51" s="161">
+        <v>-135380.74219829985</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="160" t="s">
         <v>130</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="218">
-        <v>45000</v>
-      </c>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="23">
-        <f>SUM(C24:C29)</f>
-        <v>487551.05699999997</v>
-      </c>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="43">
-        <f>+C30+C23</f>
-        <v>1342745.4069999999</v>
-      </c>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C32" s="24"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="24"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="33"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="34"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="34"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C37" s="25"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="215" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" s="215"/>
-      <c r="C38" s="216">
-        <v>1000000</v>
-      </c>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C39" s="25"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14">
-        <f>+C34+C35+C36+C39</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19">
-        <f>+C40+C31</f>
-        <v>1342745.4069999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="C45" s="162"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="C46" s="162"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="163" t="s">
-        <v>117</v>
-      </c>
-      <c r="B47" s="161"/>
-      <c r="C47" s="164">
-        <v>-135380.74219829985</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="163" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" s="161"/>
-      <c r="C48" s="166">
-        <f>-(C31-C29)</f>
-        <v>-1342745.4069999999</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="163" t="s">
+      <c r="B52" s="158"/>
+      <c r="C52" s="163">
+        <f>-(C35-C33)</f>
+        <v>-1402097.4069999999</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="161"/>
-      <c r="C49" s="208">
+      <c r="B53" s="158"/>
+      <c r="C53" s="205">
         <f>'prorrateo '!F31</f>
-        <v>2012565.1348063203</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="167"/>
-      <c r="C50" s="168"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="165" t="s">
+        <v>2194116.7546521635</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="164"/>
+      <c r="C54" s="165"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="160"/>
-      <c r="C51" s="169">
-        <f>SUM(C45:C49)</f>
-        <v>534438.98560802056</v>
-      </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="220"/>
-      <c r="B53" s="220"/>
-      <c r="C53" s="220"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="221"/>
-      <c r="B54" s="221"/>
-      <c r="C54" s="221"/>
-    </row>
-    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
+      <c r="B55" s="157"/>
+      <c r="C55" s="166">
+        <f>SUM(C49:C53)</f>
+        <v>656638.60545386374</v>
+      </c>
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="10"/>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="216"/>
+      <c r="B57" s="216"/>
+      <c r="C57" s="216"/>
+      <c r="F57" s="44"/>
+    </row>
+    <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="217"/>
+      <c r="B58" s="217"/>
+      <c r="C58" s="217"/>
+    </row>
+    <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29"/>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
+      <c r="B59" s="27"/>
+      <c r="C59" s="29"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="31">
-        <f>-C40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="31"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="28"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="32"/>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="171"/>
-      <c r="C59" s="172">
-        <f>SUM(C55:C58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="31">
+        <f>-C44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="31"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="32"/>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="168"/>
+      <c r="C63" s="169">
+        <f>SUM(C59:C62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="A57:C58"/>
   </mergeCells>
+  <phoneticPr fontId="32" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
@@ -2382,27 +2440,27 @@
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="222">
+      <c r="B1" s="218">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="144">
+      <c r="C1" s="218"/>
+      <c r="D1" s="141">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="224">
+      <c r="G1" s="220">
         <v>1000000</v>
       </c>
-      <c r="H1" s="224"/>
-    </row>
-    <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="220"/>
+    </row>
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>27</v>
       </c>
@@ -2440,7 +2498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>32</v>
       </c>
@@ -2456,7 +2514,7 @@
       <c r="E3" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F3" s="211">
+      <c r="F3" s="208">
         <f>E3</f>
         <v>124487.04578100001</v>
       </c>
@@ -2482,7 +2540,7 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>34</v>
       </c>
@@ -2498,7 +2556,7 @@
       <c r="E4" s="131">
         <v>123999.816639</v>
       </c>
-      <c r="F4" s="211">
+      <c r="F4" s="208">
         <f t="shared" ref="F4:F18" si="0">E4</f>
         <v>123999.816639</v>
       </c>
@@ -2524,7 +2582,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
@@ -2538,16 +2596,19 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="131">
-        <v>198058.75731935998</v>
-      </c>
-      <c r="F5" s="211"/>
+        <v>328762.85139613436</v>
+      </c>
+      <c r="F5" s="208">
+        <f>E5-50400*2-13326</f>
+        <v>214636.85139613436</v>
+      </c>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
-        <v>198058.75731935998</v>
+        <v>114126</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
-        <v>7922.3502927743993</v>
+        <v>4565.04</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
@@ -2560,10 +2621,10 @@
       <c r="K5" s="56"/>
       <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>328762.85139613436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>241472.783784</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>39</v>
       </c>
@@ -2575,19 +2636,19 @@
         <v>5.21</v>
       </c>
       <c r="E6" s="131">
-        <v>126923.19149100001</v>
-      </c>
-      <c r="F6" s="211">
-        <f>E6-52100</f>
-        <v>74823.191491000005</v>
+        <v>181107.19149100001</v>
+      </c>
+      <c r="F6" s="208">
+        <f>E6</f>
+        <v>181107.19149100001</v>
       </c>
       <c r="G6" s="56">
         <f t="shared" si="1"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="H6" s="56">
         <f t="shared" si="2"/>
-        <v>2084</v>
+        <v>0</v>
       </c>
       <c r="I6" s="56">
         <f t="shared" si="3"/>
@@ -2600,10 +2661,11 @@
       <c r="K6" s="56"/>
       <c r="L6" s="57">
         <f t="shared" si="5"/>
-        <v>181107.19149100001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>126923.19149100001</v>
+      </c>
+      <c r="O6" s="226"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>36</v>
       </c>
@@ -2617,11 +2679,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="131">
-        <v>200809.57339324002</v>
-      </c>
-      <c r="F7" s="211">
+        <v>124487.04578100001</v>
+      </c>
+      <c r="F7" s="208">
         <f>E7</f>
-        <v>200809.57339324002</v>
+        <v>124487.04578100001</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" si="1"/>
@@ -2644,8 +2706,9 @@
         <f t="shared" si="5"/>
         <v>124487.04578100001</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O7" s="226"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>42</v>
       </c>
@@ -2659,7 +2722,7 @@
       <c r="E8" s="131">
         <v>123999.816639</v>
       </c>
-      <c r="F8" s="211">
+      <c r="F8" s="208">
         <f>E8</f>
         <v>123999.816639</v>
       </c>
@@ -2685,7 +2748,7 @@
         <v>123999.816639</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>44</v>
       </c>
@@ -2699,7 +2762,7 @@
       <c r="E9" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F9" s="211">
+      <c r="F9" s="208">
         <f t="shared" si="0"/>
         <v>124487.04578100001</v>
       </c>
@@ -2724,47 +2787,48 @@
         <f t="shared" si="5"/>
         <v>124487.04578100001</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213" t="s">
+      <c r="O9" s="226"/>
+    </row>
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="188" t="s">
+      <c r="B10" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="189" t="s">
+      <c r="C10" s="186" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="190">
+      <c r="D10" s="187">
         <v>5.09</v>
       </c>
-      <c r="E10" s="191">
-        <v>478001.51580576197</v>
-      </c>
-      <c r="F10" s="212"/>
-      <c r="G10" s="192">
+      <c r="E10" s="188">
+        <v>621121.39307699248</v>
+      </c>
+      <c r="F10" s="209"/>
+      <c r="G10" s="189">
         <f t="shared" si="1"/>
-        <v>478001.51580576197</v>
-      </c>
-      <c r="H10" s="192">
+        <v>621121.39307699248</v>
+      </c>
+      <c r="H10" s="189">
         <f t="shared" si="2"/>
-        <v>19120.060632230477</v>
-      </c>
-      <c r="I10" s="192">
+        <v>24844.855723079701</v>
+      </c>
+      <c r="I10" s="189">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J10" s="192">
+      <c r="J10" s="189">
         <f t="shared" si="4"/>
         <v>50900</v>
       </c>
-      <c r="K10" s="192"/>
-      <c r="L10" s="193">
+      <c r="K10" s="189"/>
+      <c r="L10" s="190">
         <f t="shared" si="5"/>
-        <v>621121.39307699248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>769966.0654390722</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>112</v>
       </c>
@@ -2778,7 +2842,7 @@
       <c r="E11" s="131">
         <v>122781.74378399999</v>
       </c>
-      <c r="F11" s="211">
+      <c r="F11" s="208">
         <f>E11</f>
         <v>122781.74378399999</v>
       </c>
@@ -2804,7 +2868,7 @@
         <v>122781.74378399999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>49</v>
       </c>
@@ -2818,7 +2882,7 @@
       <c r="E12" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F12" s="211">
+      <c r="F12" s="208">
         <f t="shared" si="0"/>
         <v>126923.19149100001</v>
       </c>
@@ -2844,7 +2908,7 @@
         <v>126923.19149100001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>51</v>
       </c>
@@ -2860,7 +2924,7 @@
       <c r="E13" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F13" s="211">
+      <c r="F13" s="208">
         <f>E13</f>
         <v>124487.04578100001</v>
       </c>
@@ -2886,49 +2950,46 @@
         <v>124487.04578100001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="141" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="65" t="s">
+      <c r="B14" s="227" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="142">
+      <c r="D14" s="187">
         <v>5.09</v>
       </c>
-      <c r="E14" s="131">
-        <v>200023.62594356001</v>
-      </c>
-      <c r="F14" s="211">
-        <f>130134.19-F25</f>
-        <v>87693.027717279998</v>
-      </c>
-      <c r="G14" s="66">
+      <c r="E14" s="188">
+        <v>240823.6387943312</v>
+      </c>
+      <c r="F14" s="209"/>
+      <c r="G14" s="189">
         <f t="shared" si="1"/>
-        <v>112330.59822628001</v>
-      </c>
-      <c r="H14" s="66">
+        <v>240823.6387943312</v>
+      </c>
+      <c r="H14" s="189">
         <f t="shared" si="2"/>
-        <v>4493.2239290512007</v>
-      </c>
-      <c r="I14" s="66">
+        <v>9632.9455517732476</v>
+      </c>
+      <c r="I14" s="189">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="189">
         <f t="shared" si="4"/>
         <v>50900</v>
       </c>
-      <c r="K14" s="66"/>
-      <c r="L14" s="143">
+      <c r="K14" s="189"/>
+      <c r="L14" s="190">
         <f t="shared" si="5"/>
-        <v>240823.6387943312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>374456.40098510444</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>55</v>
       </c>
@@ -2942,16 +3003,16 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="131">
-        <v>122781.74378399999</v>
-      </c>
-      <c r="F15" s="211"/>
+        <v>250474.75731935998</v>
+      </c>
+      <c r="F15" s="208"/>
       <c r="G15" s="56">
         <f t="shared" si="1"/>
-        <v>122781.74378399999</v>
+        <v>250474.75731935998</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>4911.2697513599996</v>
+        <v>10018.990292774399</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
@@ -2964,10 +3025,10 @@
       <c r="K15" s="56"/>
       <c r="L15" s="57">
         <f t="shared" si="5"/>
-        <v>250474.75731935998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>383275.49139613437</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>58</v>
       </c>
@@ -2981,19 +3042,19 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="131">
-        <v>204739.31064164001</v>
-      </c>
-      <c r="F16" s="211">
-        <f>E16-52100</f>
-        <v>152639.31064164001</v>
+        <v>181107.19149100001</v>
+      </c>
+      <c r="F16" s="208">
+        <f>E16</f>
+        <v>181107.19149100001</v>
       </c>
       <c r="G16" s="56">
         <f t="shared" si="1"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="2"/>
-        <v>2084</v>
+        <v>0</v>
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
@@ -3006,7 +3067,7 @@
       <c r="K16" s="56"/>
       <c r="L16" s="57">
         <f t="shared" si="5"/>
-        <v>181107.19149100001</v>
+        <v>126923.19149100001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3023,7 +3084,7 @@
       <c r="E17" s="131">
         <v>122781.74378399999</v>
       </c>
-      <c r="F17" s="211">
+      <c r="F17" s="208">
         <f t="shared" si="0"/>
         <v>122781.74378399999</v>
       </c>
@@ -3063,7 +3124,7 @@
       <c r="E18" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F18" s="211">
+      <c r="F18" s="208">
         <f t="shared" si="0"/>
         <v>126923.19149100001</v>
       </c>
@@ -3103,7 +3164,7 @@
       <c r="E19" s="131">
         <v>180274.78253999999</v>
       </c>
-      <c r="F19" s="211">
+      <c r="F19" s="208">
         <f>E19</f>
         <v>180274.78253999999</v>
       </c>
@@ -3130,42 +3191,42 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="187"/>
-      <c r="B20" s="188" t="s">
+      <c r="A20" s="184"/>
+      <c r="B20" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="189" t="s">
+      <c r="C20" s="186" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="190">
+      <c r="D20" s="187">
         <v>1.08</v>
       </c>
-      <c r="E20" s="191">
-        <v>101422.71848137975</v>
-      </c>
-      <c r="F20" s="212">
-        <v>0</v>
-      </c>
-      <c r="G20" s="192">
+      <c r="E20" s="188">
+        <v>131790.00088863494</v>
+      </c>
+      <c r="F20" s="209">
+        <v>0</v>
+      </c>
+      <c r="G20" s="189">
         <f t="shared" si="1"/>
-        <v>101422.71848137975</v>
-      </c>
-      <c r="H20" s="192">
+        <v>131790.00088863494</v>
+      </c>
+      <c r="H20" s="189">
         <f t="shared" si="2"/>
-        <v>4056.9087392551901</v>
-      </c>
-      <c r="I20" s="192">
+        <v>5271.600035545398</v>
+      </c>
+      <c r="I20" s="189">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J20" s="192">
+      <c r="J20" s="189">
         <f t="shared" si="4"/>
         <v>10800</v>
       </c>
-      <c r="K20" s="192"/>
-      <c r="L20" s="193">
+      <c r="K20" s="189"/>
+      <c r="L20" s="190">
         <f t="shared" si="5"/>
-        <v>131790.00088863494</v>
+        <v>163371.97459218031</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3180,19 +3241,19 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="131">
-        <v>42441.162282719997</v>
-      </c>
-      <c r="F21" s="211">
-        <f>E21-10800</f>
-        <v>31641.162282719997</v>
+        <v>37542.373668</v>
+      </c>
+      <c r="F21" s="208">
+        <f>E21</f>
+        <v>37542.373668</v>
       </c>
       <c r="G21" s="56">
         <f t="shared" si="1"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="56">
         <f t="shared" si="2"/>
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="I21" s="56">
         <f t="shared" si="3"/>
@@ -3205,44 +3266,44 @@
       <c r="K21" s="66"/>
       <c r="L21" s="57">
         <f t="shared" si="5"/>
-        <v>37542.373668</v>
+        <v>26310.373668</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="145"/>
-      <c r="B22" s="146"/>
-      <c r="C22" s="147" t="s">
+      <c r="A22" s="142"/>
+      <c r="B22" s="143"/>
+      <c r="C22" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="148">
+      <c r="D22" s="145">
         <v>1.08</v>
       </c>
-      <c r="E22" s="149">
-        <v>101422.71848137975</v>
-      </c>
-      <c r="F22" s="217">
-        <v>0</v>
-      </c>
-      <c r="G22" s="150">
+      <c r="E22" s="146">
+        <v>131790.00088863494</v>
+      </c>
+      <c r="F22" s="214">
+        <v>0</v>
+      </c>
+      <c r="G22" s="147">
         <f t="shared" si="1"/>
-        <v>101422.71848137975</v>
-      </c>
-      <c r="H22" s="150">
+        <v>131790.00088863494</v>
+      </c>
+      <c r="H22" s="147">
         <f t="shared" si="2"/>
-        <v>4056.9087392551901</v>
-      </c>
-      <c r="I22" s="150">
+        <v>5271.600035545398</v>
+      </c>
+      <c r="I22" s="147">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J22" s="150">
+      <c r="J22" s="147">
         <f t="shared" si="4"/>
         <v>10800</v>
       </c>
-      <c r="K22" s="150"/>
-      <c r="L22" s="151">
+      <c r="K22" s="147"/>
+      <c r="L22" s="148">
         <f t="shared" si="5"/>
-        <v>131790.00088863494</v>
+        <v>163371.97459218031</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3257,16 +3318,19 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="131">
-        <v>42441.162282719997</v>
-      </c>
-      <c r="F23" s="211"/>
+        <v>70449.182442028789</v>
+      </c>
+      <c r="F23" s="208">
+        <f>E23-10800*2</f>
+        <v>48849.182442028789</v>
+      </c>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
-        <v>42441.162282719997</v>
+        <v>21600</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>1697.6464913088</v>
+        <v>864</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
@@ -3279,7 +3343,7 @@
       <c r="K23" s="56"/>
       <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>70449.182442028789</v>
+        <v>48774.373668</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3298,7 +3362,7 @@
       <c r="E24" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F24" s="211">
+      <c r="F24" s="208">
         <f>E24</f>
         <v>26310.373668</v>
       </c>
@@ -3336,19 +3400,16 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="131">
-        <v>42441.162282719997</v>
-      </c>
-      <c r="F25" s="211">
-        <f>E25</f>
-        <v>42441.162282719997</v>
-      </c>
+        <v>26310.373668</v>
+      </c>
+      <c r="F25" s="208"/>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26310.373668</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1052.41494672</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
@@ -3361,7 +3422,7 @@
       <c r="K25" s="56"/>
       <c r="L25" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>53673.162282719997</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3378,7 +3439,7 @@
       <c r="E26" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F26" s="211">
+      <c r="F26" s="208">
         <f t="shared" ref="F26:F28" si="6">E26</f>
         <v>26310.373668</v>
       </c>
@@ -3418,7 +3479,7 @@
       <c r="E27" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F27" s="211">
+      <c r="F27" s="208">
         <f t="shared" si="6"/>
         <v>26310.373668</v>
       </c>
@@ -3461,11 +3522,11 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="131">
-        <v>42441.162282719997</v>
-      </c>
-      <c r="F28" s="211">
+        <v>26310.373668</v>
+      </c>
+      <c r="F28" s="208">
         <f t="shared" si="6"/>
-        <v>42441.162282719997</v>
+        <v>26310.373668</v>
       </c>
       <c r="G28" s="56">
         <f t="shared" si="1"/>
@@ -3503,16 +3564,16 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="131">
-        <v>26310.373668</v>
-      </c>
-      <c r="F29" s="211"/>
+        <v>53673.162282719997</v>
+      </c>
+      <c r="F29" s="208"/>
       <c r="G29" s="56">
         <f t="shared" si="1"/>
-        <v>26310.373668</v>
+        <v>53673.162282719997</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>1052.41494672</v>
+        <v>2146.9264913088</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
@@ -3525,7 +3586,7 @@
       <c r="K29" s="56"/>
       <c r="L29" s="57">
         <f t="shared" si="5"/>
-        <v>53673.162282719997</v>
+        <v>82130.462442028787</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3555,7 +3616,7 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>2012565.1348063203</v>
+        <v>2194116.7546521635</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
@@ -3570,69 +3631,67 @@
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>3785826.0815708381</v>
+        <v>4091523.4099954218</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="223" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="223"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="223"/>
-      <c r="K33" s="223"/>
-      <c r="L33" s="223"/>
+      <c r="A33" s="219"/>
+      <c r="B33" s="219"/>
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="223"/>
-      <c r="B34" s="223"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="223"/>
-      <c r="I34" s="223"/>
-      <c r="J34" s="223"/>
-      <c r="K34" s="223"/>
-      <c r="L34" s="223"/>
+      <c r="A34" s="219"/>
+      <c r="B34" s="219"/>
+      <c r="C34" s="219"/>
+      <c r="D34" s="219"/>
+      <c r="E34" s="219"/>
+      <c r="F34" s="219"/>
+      <c r="G34" s="219"/>
+      <c r="H34" s="219"/>
+      <c r="I34" s="219"/>
+      <c r="J34" s="219"/>
+      <c r="K34" s="219"/>
+      <c r="L34" s="219"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="223"/>
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="223"/>
-      <c r="I35" s="223"/>
-      <c r="J35" s="223"/>
-      <c r="K35" s="223"/>
-      <c r="L35" s="223"/>
+      <c r="A35" s="219"/>
+      <c r="B35" s="219"/>
+      <c r="C35" s="219"/>
+      <c r="D35" s="219"/>
+      <c r="E35" s="219"/>
+      <c r="F35" s="219"/>
+      <c r="G35" s="219"/>
+      <c r="H35" s="219"/>
+      <c r="I35" s="219"/>
+      <c r="J35" s="219"/>
+      <c r="K35" s="219"/>
+      <c r="L35" s="219"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="223"/>
-      <c r="B36" s="223"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="223"/>
-      <c r="K36" s="223"/>
-      <c r="L36" s="223"/>
+      <c r="A36" s="219"/>
+      <c r="B36" s="219"/>
+      <c r="C36" s="219"/>
+      <c r="D36" s="219"/>
+      <c r="E36" s="219"/>
+      <c r="F36" s="219"/>
+      <c r="G36" s="219"/>
+      <c r="H36" s="219"/>
+      <c r="I36" s="219"/>
+      <c r="J36" s="219"/>
+      <c r="K36" s="219"/>
+      <c r="L36" s="219"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3672,113 +3731,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="221" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="227"/>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="223"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="177"/>
-      <c r="I2" s="176"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="176"/>
-      <c r="L2" s="176"/>
-      <c r="M2" s="176"/>
-      <c r="N2" s="176"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="173"/>
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="173"/>
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="176" t="s">
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="173" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="176"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="176"/>
-      <c r="M4" s="176"/>
-      <c r="N4" s="176"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="173"/>
+      <c r="M4" s="173"/>
+      <c r="N4" s="173"/>
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="178"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="175"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
+      <c r="L5" s="173"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="173"/>
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
-      <c r="C6" s="176"/>
+      <c r="C6" s="173"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="176"/>
-      <c r="L6" s="176"/>
-      <c r="M6" s="176"/>
-      <c r="N6" s="176"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="173"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="173"/>
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
@@ -3787,25 +3846,25 @@
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="230">
+      <c r="C7" s="215">
         <v>662901.94999999995</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176" t="s">
+      <c r="E7" s="173"/>
+      <c r="F7" s="173" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="176"/>
-      <c r="H7" s="177"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176" t="str">
+      <c r="G7" s="173"/>
+      <c r="H7" s="174"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 14/08</v>
       </c>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="176"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="173"/>
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
@@ -3823,13 +3882,13 @@
       <c r="J8" s="80"/>
       <c r="K8" s="88">
         <f>C8-J38</f>
-        <v>-227016.12285000001</v>
-      </c>
-      <c r="L8" s="229">
+        <v>-290631.84495</v>
+      </c>
+      <c r="L8" s="225">
         <f>C7-J38</f>
-        <v>435885.82714999991</v>
-      </c>
-      <c r="M8" s="229"/>
+        <v>372270.10504999995</v>
+      </c>
+      <c r="M8" s="225"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3896,42 +3955,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="104">
-        <v>3122.7</v>
+        <v>3448</v>
       </c>
       <c r="G10" s="105">
-        <v>3448</v>
+        <v>3850.8</v>
       </c>
       <c r="H10" s="106">
         <f>G10-F10</f>
-        <v>325.30000000000018</v>
+        <v>402.80000000000018</v>
       </c>
       <c r="I10" s="107">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>22.771000000000015</v>
+        <v>28.196000000000016</v>
       </c>
       <c r="J10" s="118">
         <f>M10*93.787</f>
-        <v>30508.911100000019</v>
+        <v>37777.40360000002</v>
       </c>
       <c r="K10" s="108">
         <f>K8*E10%</f>
-        <v>-11600.523877635002</v>
+        <v>-14851.287276945002</v>
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>22273.765767364996</v>
+        <v>19023.002368055</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
-        <v>325.30000000000018</v>
+        <v>402.80000000000018</v>
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>52782.676867365015</v>
+        <v>56800.40596805502</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>177269.72264836502</v>
+        <v>181287.45174905504</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3952,42 +4011,42 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="104">
-        <v>3093.6</v>
+        <v>3296</v>
       </c>
       <c r="G11" s="105">
-        <v>3296</v>
+        <v>3632.1</v>
       </c>
       <c r="H11" s="106">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>202.40000000000009</v>
+        <v>336.09999999999991</v>
       </c>
       <c r="I11" s="107">
         <f t="shared" si="0"/>
-        <v>14.168000000000008</v>
+        <v>23.526999999999997</v>
       </c>
       <c r="J11" s="118">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>18982.48880000001</v>
+        <v>31521.810699999995</v>
       </c>
       <c r="K11" s="108">
         <f>K8*E11%</f>
-        <v>-11555.120653065002</v>
+        <v>-14793.160907955</v>
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>22186.588601934993</v>
+        <v>18948.548347044998</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>202.40000000000009</v>
+        <v>336.09999999999991</v>
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>41169.077401935006</v>
+        <v>50470.359047044993</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>165168.894040935</v>
+        <v>174470.175686045</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4008,42 +4067,42 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="104">
-        <v>1314.5</v>
+        <v>1366.3</v>
       </c>
       <c r="G12" s="105">
-        <v>1366.3</v>
+        <v>1394.3</v>
       </c>
       <c r="H12" s="106">
         <f t="shared" si="1"/>
-        <v>51.799999999999955</v>
+        <v>28</v>
       </c>
       <c r="I12" s="107">
         <f t="shared" si="0"/>
-        <v>3.6259999999999972</v>
+        <v>1.9600000000000002</v>
       </c>
       <c r="J12" s="118">
         <f t="shared" si="2"/>
-        <v>4858.1665999999959</v>
+        <v>2626.0360000000001</v>
       </c>
       <c r="K12" s="108">
         <f>K8*E12%</f>
-        <v>-11441.612591640001</v>
+        <v>-14647.84498548</v>
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>21968.645688359993</v>
+        <v>18762.41329452</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
-        <v>51.799999999999955</v>
+        <v>28</v>
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>26826.81228835999</v>
+        <v>21388.44929452</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>355589.66368449433</v>
+        <v>262861.23307851999</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4057,52 +4116,52 @@
       <c r="B13" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="179" t="s">
+      <c r="C13" s="176" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="180">
+      <c r="E13" s="177">
         <v>5.21</v>
       </c>
       <c r="F13" s="104">
-        <v>791.8</v>
+        <v>883.5</v>
       </c>
       <c r="G13" s="105">
-        <v>883.5</v>
+        <v>981.5</v>
       </c>
       <c r="H13" s="106">
         <f t="shared" si="1"/>
-        <v>91.700000000000045</v>
-      </c>
-      <c r="I13" s="181">
+        <v>98</v>
+      </c>
+      <c r="I13" s="178">
         <f t="shared" si="0"/>
-        <v>6.419000000000004</v>
+        <v>6.86</v>
       </c>
       <c r="J13" s="118">
         <f t="shared" si="2"/>
-        <v>8600.2679000000044</v>
-      </c>
-      <c r="K13" s="182">
+        <v>9191.1260000000002</v>
+      </c>
+      <c r="K13" s="179">
         <f>K8*E13%</f>
-        <v>-11827.540000485002</v>
+        <v>-15141.919121895</v>
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>22709.651594514995</v>
-      </c>
-      <c r="M13" s="183">
+        <v>19395.272473104997</v>
+      </c>
+      <c r="M13" s="180">
         <f t="shared" si="4"/>
-        <v>91.700000000000045</v>
+        <v>98</v>
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>31309.919494515001</v>
+        <v>28586.398473104997</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>212417.110985515</v>
+        <v>155509.58996410499</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4123,42 +4182,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="104">
-        <v>1435.7</v>
+        <v>1509.4</v>
       </c>
       <c r="G14" s="105">
-        <v>1509.4</v>
+        <v>1583.5</v>
       </c>
       <c r="H14" s="106">
         <f t="shared" si="1"/>
-        <v>73.700000000000045</v>
+        <v>74.099999999999909</v>
       </c>
       <c r="I14" s="107">
         <f t="shared" si="0"/>
-        <v>5.1590000000000034</v>
+        <v>5.1869999999999941</v>
       </c>
       <c r="J14" s="118">
         <f t="shared" si="2"/>
-        <v>6912.1019000000051</v>
+        <v>6949.6166999999923</v>
       </c>
       <c r="K14" s="108">
         <f>K8*E14%</f>
-        <v>-11600.523877635002</v>
+        <v>-14851.287276945002</v>
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>22273.765767364996</v>
+        <v>19023.002368055</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
-        <v>73.700000000000045</v>
+        <v>74.099999999999909</v>
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>29185.867667365001</v>
+        <v>25972.619068054992</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>153672.913448365</v>
+        <v>150459.664849055</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4179,42 +4238,42 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="104">
-        <v>2418</v>
+        <v>2581.1999999999998</v>
       </c>
       <c r="G15" s="105">
-        <v>2581.1999999999998</v>
+        <v>2726.2</v>
       </c>
       <c r="H15" s="106">
         <f t="shared" si="1"/>
-        <v>163.19999999999982</v>
+        <v>145</v>
       </c>
       <c r="I15" s="107">
         <f t="shared" si="0"/>
-        <v>11.423999999999989</v>
+        <v>10.15</v>
       </c>
       <c r="J15" s="118">
         <f t="shared" si="2"/>
-        <v>15306.038399999983</v>
+        <v>13599.115000000002</v>
       </c>
       <c r="K15" s="108">
         <f>K8*E15%</f>
-        <v>-11555.120653065002</v>
+        <v>-14793.160907955</v>
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>22186.588601934993</v>
+        <v>18948.548347044998</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
-        <v>163.19999999999982</v>
+        <v>145</v>
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>37492.627001934976</v>
+        <v>32547.663347045</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>161492.44364093497</v>
+        <v>156547.47998604499</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4234,42 +4293,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="104">
-        <v>2053.3000000000002</v>
+        <v>2155.5</v>
       </c>
       <c r="G16" s="105">
-        <v>2155.5</v>
+        <v>2244.6999999999998</v>
       </c>
       <c r="H16" s="106">
         <f t="shared" si="1"/>
-        <v>102.19999999999982</v>
+        <v>89.199999999999818</v>
       </c>
       <c r="I16" s="107">
         <f t="shared" si="0"/>
-        <v>7.1539999999999884</v>
+        <v>6.2439999999999882</v>
       </c>
       <c r="J16" s="118">
         <f t="shared" si="2"/>
-        <v>9585.0313999999835</v>
+        <v>8365.8003999999837</v>
       </c>
       <c r="K16" s="108">
         <f>K8*E16%</f>
-        <v>-11600.523877635002</v>
+        <v>-14851.287276945002</v>
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>22273.765767364996</v>
+        <v>19023.002368055</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
-        <v>102.19999999999982</v>
+        <v>89.199999999999818</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>31858.797167364981</v>
+        <v>27388.802768054986</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>156345.842948365</v>
+        <v>151875.84854905499</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4279,52 +4338,52 @@
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="194" t="s">
+      <c r="C17" s="191" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="195" t="s">
+      <c r="D17" s="192" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="196">
+      <c r="E17" s="193">
         <v>5.09</v>
       </c>
-      <c r="F17" s="197">
-        <v>3139.2</v>
-      </c>
-      <c r="G17" s="198">
+      <c r="F17" s="194">
         <v>3253.7</v>
       </c>
-      <c r="H17" s="199">
+      <c r="G17" s="195">
+        <v>3290.2</v>
+      </c>
+      <c r="H17" s="196">
         <f t="shared" si="1"/>
-        <v>114.5</v>
-      </c>
-      <c r="I17" s="200">
+        <v>36.5</v>
+      </c>
+      <c r="I17" s="197">
         <f t="shared" si="0"/>
-        <v>8.0150000000000006</v>
-      </c>
-      <c r="J17" s="201">
+        <v>2.5550000000000002</v>
+      </c>
+      <c r="J17" s="198">
         <f t="shared" si="2"/>
-        <v>10738.611500000001</v>
-      </c>
-      <c r="K17" s="202">
+        <v>3423.2255</v>
+      </c>
+      <c r="K17" s="199">
         <f>K8*E17%</f>
-        <v>-11555.120653065002</v>
-      </c>
-      <c r="L17" s="203">
+        <v>-14793.160907955</v>
+      </c>
+      <c r="L17" s="200">
         <f t="shared" si="3"/>
-        <v>22186.588601934993</v>
-      </c>
-      <c r="M17" s="204">
+        <v>18948.548347044998</v>
+      </c>
+      <c r="M17" s="201">
         <f t="shared" si="4"/>
-        <v>114.5</v>
-      </c>
-      <c r="N17" s="199">
+        <v>36.5</v>
+      </c>
+      <c r="N17" s="196">
         <f t="shared" si="5"/>
-        <v>32925.200101934992</v>
+        <v>22371.773847044999</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>654046.59317892743</v>
+        <v>792337.83928611723</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4344,42 +4403,42 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="104">
-        <v>1790</v>
+        <v>1888.2</v>
       </c>
       <c r="G18" s="105">
-        <v>1888.2</v>
+        <v>1987.7</v>
       </c>
       <c r="H18" s="106">
         <f t="shared" si="1"/>
-        <v>98.200000000000045</v>
+        <v>99.5</v>
       </c>
       <c r="I18" s="107">
         <f t="shared" si="0"/>
-        <v>6.8740000000000041</v>
+        <v>6.9650000000000007</v>
       </c>
       <c r="J18" s="118">
         <f t="shared" si="2"/>
-        <v>9209.8834000000043</v>
+        <v>9331.8065000000006</v>
       </c>
       <c r="K18" s="108">
         <f>K8*E18%</f>
-        <v>-11441.612591640001</v>
+        <v>-14647.84498548</v>
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>21968.645688359993</v>
+        <v>18762.41329452</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
-        <v>98.200000000000045</v>
+        <v>99.5</v>
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>31178.529088359996</v>
+        <v>28094.219794520002</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>153960.27287235999</v>
+        <v>150875.96357851999</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4399,42 +4458,42 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="104">
-        <v>2998.2</v>
+        <v>3235.4</v>
       </c>
       <c r="G19" s="105">
-        <v>3235.4</v>
+        <v>3555.8</v>
       </c>
       <c r="H19" s="106">
         <f t="shared" si="1"/>
-        <v>237.20000000000027</v>
+        <v>320.40000000000009</v>
       </c>
       <c r="I19" s="107">
         <f t="shared" si="0"/>
-        <v>16.604000000000021</v>
+        <v>22.428000000000008</v>
       </c>
       <c r="J19" s="118">
         <f t="shared" si="2"/>
-        <v>22246.276400000028</v>
+        <v>30049.354800000012</v>
       </c>
       <c r="K19" s="108">
         <f>K8*E19%</f>
-        <v>-11827.540000485002</v>
+        <v>-15141.919121895</v>
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>22709.651594514995</v>
+        <v>19395.272473104997</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
-        <v>237.20000000000027</v>
+        <v>320.40000000000009</v>
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>44955.927994515019</v>
+        <v>49444.627273105012</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>171879.11948551502</v>
+        <v>176367.81876410503</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4454,42 +4513,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="104">
-        <v>4665.5</v>
+        <v>4902.5</v>
       </c>
       <c r="G20" s="105">
-        <v>4902.5</v>
+        <v>5174.2</v>
       </c>
       <c r="H20" s="106">
         <f t="shared" si="1"/>
-        <v>237</v>
+        <v>271.69999999999982</v>
       </c>
       <c r="I20" s="107">
         <f t="shared" si="0"/>
-        <v>16.59</v>
+        <v>19.018999999999988</v>
       </c>
       <c r="J20" s="118">
         <f t="shared" si="2"/>
-        <v>22227.519</v>
+        <v>25481.927899999984</v>
       </c>
       <c r="K20" s="108">
         <f>K8*E20%</f>
-        <v>-11600.523877635002</v>
+        <v>-14851.287276945002</v>
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>22273.765767364996</v>
+        <v>19023.002368055</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
-        <v>237</v>
+        <v>271.69999999999982</v>
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>44501.284767364996</v>
+        <v>44504.930268054988</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>168988.33054836502</v>
+        <v>168991.976049055</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4499,52 +4558,52 @@
       <c r="B21" s="91">
         <v>13</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="102" t="s">
+      <c r="D21" s="192" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="103">
+      <c r="E21" s="193">
         <v>5.09</v>
       </c>
-      <c r="F21" s="104">
-        <v>3467.1</v>
-      </c>
-      <c r="G21" s="105">
+      <c r="F21" s="194">
         <v>3467.7</v>
       </c>
-      <c r="H21" s="106">
+      <c r="G21" s="195">
+        <v>3739.6</v>
+      </c>
+      <c r="H21" s="196">
         <f t="shared" si="1"/>
-        <v>0.59999999999990905</v>
-      </c>
-      <c r="I21" s="107">
+        <v>271.90000000000009</v>
+      </c>
+      <c r="I21" s="197">
         <f t="shared" si="0"/>
-        <v>4.199999999999364E-2</v>
-      </c>
-      <c r="J21" s="118">
+        <v>19.033000000000008</v>
+      </c>
+      <c r="J21" s="198">
         <f t="shared" si="2"/>
-        <v>56.272199999991471</v>
-      </c>
-      <c r="K21" s="108">
+        <v>25500.685300000012</v>
+      </c>
+      <c r="K21" s="199">
         <f>K8*E21%</f>
-        <v>-11555.120653065002</v>
-      </c>
-      <c r="L21" s="129">
+        <v>-14793.160907955</v>
+      </c>
+      <c r="L21" s="200">
         <f t="shared" si="3"/>
-        <v>22186.588601934993</v>
-      </c>
-      <c r="M21" s="109">
+        <v>18948.548347044998</v>
+      </c>
+      <c r="M21" s="201">
         <f t="shared" si="4"/>
-        <v>0.59999999999990905</v>
-      </c>
-      <c r="N21" s="106">
+        <v>271.90000000000009</v>
+      </c>
+      <c r="N21" s="196">
         <f t="shared" si="5"/>
-        <v>22242.860801934985</v>
+        <v>44449.23364704501</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>263066.49959626619</v>
+        <v>418905.63463214948</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4564,42 +4623,42 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="104">
-        <v>2097.9</v>
+        <v>2198.0500000000002</v>
       </c>
       <c r="G22" s="105">
-        <v>2198.0500000000002</v>
+        <v>2282.3000000000002</v>
       </c>
       <c r="H22" s="106">
         <f t="shared" si="1"/>
-        <v>100.15000000000009</v>
+        <v>84.25</v>
       </c>
       <c r="I22" s="107">
         <f t="shared" si="0"/>
-        <v>7.0105000000000066</v>
+        <v>5.8975000000000009</v>
       </c>
       <c r="J22" s="118">
         <f t="shared" si="2"/>
-        <v>9392.7680500000097</v>
+        <v>7901.5547500000002</v>
       </c>
       <c r="K22" s="108">
         <f>K8*E22%</f>
-        <v>-11441.612591640001</v>
+        <v>-14647.84498548</v>
       </c>
       <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>21968.645688359993</v>
+        <v>18762.41329452</v>
       </c>
       <c r="M22" s="109">
         <f t="shared" si="4"/>
-        <v>100.15000000000009</v>
+        <v>84.25</v>
       </c>
       <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>31361.413738360003</v>
+        <v>26663.968044519999</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>281836.17105771997</v>
+        <v>409939.45944065438</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4619,42 +4678,42 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="104">
-        <v>4222.8</v>
+        <v>4358.6000000000004</v>
       </c>
       <c r="G23" s="105">
-        <v>4358.6000000000004</v>
+        <v>4515.3</v>
       </c>
       <c r="H23" s="106">
         <f t="shared" si="1"/>
-        <v>135.80000000000018</v>
+        <v>156.69999999999982</v>
       </c>
       <c r="I23" s="107">
         <f t="shared" si="0"/>
-        <v>9.5060000000000144</v>
+        <v>10.968999999999989</v>
       </c>
       <c r="J23" s="118">
         <f t="shared" si="2"/>
-        <v>12736.274600000017</v>
+        <v>14696.422899999983</v>
       </c>
       <c r="K23" s="108">
         <f>K8*E23%</f>
-        <v>-11827.540000485002</v>
+        <v>-15141.919121895</v>
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>22709.651594514995</v>
+        <v>19395.272473104997</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
-        <v>135.80000000000018</v>
+        <v>156.69999999999982</v>
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>35445.926194515014</v>
+        <v>34091.69537310498</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>216553.11768551503</v>
+        <v>161014.88686410498</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4674,42 +4733,42 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="104">
-        <v>1529.3</v>
+        <v>1563.2</v>
       </c>
       <c r="G24" s="105">
-        <v>1563.2</v>
+        <v>1624.6</v>
       </c>
       <c r="H24" s="106">
         <f t="shared" si="1"/>
-        <v>33.900000000000091</v>
+        <v>61.399999999999864</v>
       </c>
       <c r="I24" s="107">
         <f t="shared" si="0"/>
-        <v>2.3730000000000064</v>
+        <v>4.2979999999999912</v>
       </c>
       <c r="J24" s="118">
         <f t="shared" si="2"/>
-        <v>3179.3793000000087</v>
+        <v>5758.5217999999877</v>
       </c>
       <c r="K24" s="108">
         <f>K8*E24%</f>
-        <v>-11441.612591640001</v>
+        <v>-14647.84498548</v>
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>21968.645688359993</v>
+        <v>18762.41329452</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
-        <v>33.900000000000091</v>
+        <v>61.399999999999864</v>
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>25148.024988360001</v>
+        <v>24520.935094519988</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>147929.76877236</v>
+        <v>147302.67887851998</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4729,42 +4788,42 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="104">
-        <v>1452.3</v>
+        <v>1527.7</v>
       </c>
       <c r="G25" s="105">
-        <v>1527.7</v>
+        <v>1613.2</v>
       </c>
       <c r="H25" s="106">
         <f t="shared" si="1"/>
-        <v>75.400000000000091</v>
+        <v>85.5</v>
       </c>
       <c r="I25" s="107">
         <f t="shared" si="0"/>
-        <v>5.2780000000000067</v>
+        <v>5.9850000000000003</v>
       </c>
       <c r="J25" s="118">
         <f t="shared" si="2"/>
-        <v>7071.5398000000087</v>
+        <v>8018.7885000000006</v>
       </c>
       <c r="K25" s="108">
         <f>K8*E25%</f>
-        <v>-11827.540000485002</v>
+        <v>-15141.919121895</v>
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>22709.651594514995</v>
+        <v>19395.272473104997</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
-        <v>75.400000000000091</v>
+        <v>85.5</v>
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>29781.191394515005</v>
+        <v>27414.060973104999</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>156704.38288551502</v>
+        <v>154337.252464105</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4784,42 +4843,42 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="104">
-        <v>7289.3</v>
+        <v>7666.8</v>
       </c>
       <c r="G26" s="105">
-        <v>7666.8</v>
+        <v>8204.6</v>
       </c>
       <c r="H26" s="106">
         <f t="shared" si="1"/>
-        <v>377.5</v>
+        <v>537.80000000000018</v>
       </c>
       <c r="I26" s="107">
         <f t="shared" si="0"/>
-        <v>26.425000000000004</v>
+        <v>37.646000000000015</v>
       </c>
       <c r="J26" s="118">
         <f t="shared" si="2"/>
-        <v>35404.592499999999</v>
+        <v>50438.648600000022</v>
       </c>
       <c r="K26" s="108">
         <f>K8*E26%</f>
-        <v>-16799.193090900004</v>
+        <v>-21506.756526300003</v>
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>32255.551209099995</v>
+        <v>27547.987773699999</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
-        <v>377.5</v>
+        <v>537.80000000000018</v>
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>67660.143709099997</v>
+        <v>77986.636373700021</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>247934.92624909998</v>
+        <v>258261.41891370001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4829,41 +4888,41 @@
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="205" t="s">
+      <c r="C27" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="206" t="s">
+      <c r="D27" s="203" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="207">
+      <c r="E27" s="204">
         <v>1.08</v>
       </c>
-      <c r="F27" s="197"/>
-      <c r="G27" s="198"/>
-      <c r="H27" s="199">
+      <c r="F27" s="194"/>
+      <c r="G27" s="195"/>
+      <c r="H27" s="196">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="200">
+      <c r="I27" s="197">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="201"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="203">
+      <c r="J27" s="198"/>
+      <c r="K27" s="199"/>
+      <c r="L27" s="200">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
-      </c>
-      <c r="M27" s="204">
-        <v>0</v>
-      </c>
-      <c r="N27" s="199">
+        <v>4020.5171345399995</v>
+      </c>
+      <c r="M27" s="201">
+        <v>0</v>
+      </c>
+      <c r="N27" s="196">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>136497.56782185493</v>
+        <v>167392.4917267203</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4871,7 +4930,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="92"/>
-      <c r="C28" s="184" t="s">
+      <c r="C28" s="181" t="s">
         <v>68</v>
       </c>
       <c r="D28" s="104"/>
@@ -4883,64 +4942,64 @@
       <c r="H28" s="106">
         <v>0</v>
       </c>
-      <c r="I28" s="185">
+      <c r="I28" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="186"/>
+      <c r="J28" s="183"/>
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>42249.940601219998</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
-      <c r="C29" s="173" t="s">
+      <c r="C29" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152">
+      <c r="D29" s="149"/>
+      <c r="E29" s="149">
         <v>1.08</v>
       </c>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="155">
+      <c r="F29" s="149"/>
+      <c r="G29" s="149"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="172"/>
+      <c r="K29" s="151"/>
+      <c r="L29" s="152">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
-      </c>
-      <c r="M29" s="156">
-        <v>0</v>
-      </c>
-      <c r="N29" s="153">
+        <v>4020.5171345399995</v>
+      </c>
+      <c r="M29" s="153">
+        <v>0</v>
+      </c>
+      <c r="N29" s="150">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>136497.56782185493</v>
+        <v>167392.4917267203</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="181" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="104"/>
@@ -4950,29 +5009,29 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="106"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="186"/>
+      <c r="I30" s="182"/>
+      <c r="J30" s="183"/>
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>75156.749375248794</v>
+        <v>52794.890802540001</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="181" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="104"/>
@@ -4982,23 +5041,23 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="106"/>
-      <c r="I31" s="185"/>
-      <c r="J31" s="186"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="183"/>
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>31017.940601219998</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5019,18 +5078,18 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>31017.940601219998</v>
+        <v>57693.679417259998</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5051,18 +5110,18 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>31017.940601219998</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5083,18 +5142,18 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>31017.940601219998</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5102,7 +5161,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="92"/>
-      <c r="C35" s="184" t="s">
+      <c r="C35" s="181" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="104"/>
@@ -5114,26 +5173,26 @@
       <c r="H35" s="106">
         <v>0</v>
       </c>
-      <c r="I35" s="185">
+      <c r="I35" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="209"/>
+      <c r="J35" s="206"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>31017.940601219998</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5141,7 +5200,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="92"/>
-      <c r="C36" s="184" t="s">
+      <c r="C36" s="181" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="104"/>
@@ -5153,26 +5212,26 @@
       <c r="H36" s="106">
         <v>0</v>
       </c>
-      <c r="I36" s="185">
+      <c r="I36" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="209"/>
+      <c r="J36" s="206"/>
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="M36" s="109">
         <v>0</v>
       </c>
       <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>4707.5669332199996</v>
+        <v>4020.5171345399995</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>58380.729215939995</v>
+        <v>86150.979576568789</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5219,17 +5278,17 @@
       <c r="I38" s="114"/>
       <c r="J38" s="119">
         <f>SUM(J10:J37)</f>
-        <v>227016.12285000001</v>
+        <v>290631.84495</v>
       </c>
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>435885.82715000008</v>
+        <v>372270.10505000007</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>662901.95000000007</v>
+        <v>662901.95000000019</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5246,7 +5305,7 @@
       <c r="H39" s="95"/>
       <c r="I39" s="96">
         <f>SUM(I10:I38)</f>
-        <v>169.43850000000009</v>
+        <v>216.91950000000006</v>
       </c>
       <c r="J39" s="128"/>
       <c r="K39" s="96"/>
@@ -5262,18 +5321,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
-      <c r="J40" s="226"/>
-      <c r="K40" s="226"/>
-      <c r="L40" s="226"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
+      <c r="C40" s="224"/>
+      <c r="D40" s="222"/>
+      <c r="E40" s="222"/>
+      <c r="F40" s="222"/>
+      <c r="G40" s="222"/>
+      <c r="H40" s="222"/>
+      <c r="I40" s="222"/>
+      <c r="J40" s="222"/>
+      <c r="K40" s="222"/>
+      <c r="L40" s="222"/>
+      <c r="M40" s="222"/>
+      <c r="N40" s="222"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -5287,20 +5346,20 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L44" s="157"/>
+      <c r="L44" s="154"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E46" s="158"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="158"/>
-      <c r="I46" s="158"/>
-      <c r="J46" s="158"/>
-      <c r="K46" s="158"/>
-      <c r="L46" s="159"/>
+      <c r="E46" s="155"/>
+      <c r="F46" s="155"/>
+      <c r="G46" s="155"/>
+      <c r="H46" s="155"/>
+      <c r="I46" s="155"/>
+      <c r="J46" s="155"/>
+      <c r="K46" s="155"/>
+      <c r="L46" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
+++ b/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1318F77-F975-4AAA-A958-C39B5485B956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8DB37-CE23-4574-B4AA-73AB57F19CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
   <si>
     <t>TOTAL</t>
   </si>
@@ -438,6 +438,10 @@
   </si>
   <si>
     <t>TSG MES 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES
+</t>
   </si>
 </sst>
 </file>
@@ -459,7 +463,7 @@
     <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,6 +684,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1142,7 +1154,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1471,6 +1483,13 @@
     <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1497,12 +1516,11 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2020,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="228">
+      <c r="C19" s="218">
         <v>350140.35</v>
       </c>
       <c r="D19" s="20"/>
@@ -2031,7 +2049,7 @@
         <v>131</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="228">
+      <c r="C20" s="218">
         <v>280000</v>
       </c>
       <c r="D20" s="20"/>
@@ -2334,15 +2352,15 @@
       <c r="C56" s="10"/>
     </row>
     <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="216"/>
-      <c r="B57" s="216"/>
-      <c r="C57" s="216"/>
+      <c r="A57" s="219"/>
+      <c r="B57" s="219"/>
+      <c r="C57" s="219"/>
       <c r="F57" s="44"/>
     </row>
     <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="217"/>
-      <c r="B58" s="217"/>
-      <c r="C58" s="217"/>
+      <c r="A58" s="220"/>
+      <c r="B58" s="220"/>
+      <c r="C58" s="220"/>
     </row>
     <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
@@ -2382,19 +2400,21 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
+      <c r="A64" s="229" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="230"/>
+      <c r="C64" s="230"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+      <c r="A65" s="230"/>
+      <c r="B65" s="230"/>
+      <c r="C65" s="230"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
+      <c r="A66" s="230"/>
+      <c r="B66" s="230"/>
+      <c r="C66" s="230"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
@@ -2402,8 +2422,9 @@
       <c r="C67" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A57:C58"/>
+    <mergeCell ref="A64:C66"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <hyperlinks>
@@ -2411,7 +2432,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2444,21 +2465,21 @@
       <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="218">
+      <c r="B1" s="221">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="218"/>
+      <c r="C1" s="221"/>
       <c r="D1" s="141">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="220">
+      <c r="G1" s="223">
         <v>1000000</v>
       </c>
-      <c r="H1" s="220"/>
+      <c r="H1" s="223"/>
     </row>
     <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2663,7 +2684,7 @@
         <f t="shared" si="5"/>
         <v>126923.19149100001</v>
       </c>
-      <c r="O6" s="226"/>
+      <c r="O6" s="216"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
@@ -2706,7 +2727,7 @@
         <f t="shared" si="5"/>
         <v>124487.04578100001</v>
       </c>
-      <c r="O7" s="226"/>
+      <c r="O7" s="216"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
@@ -2787,7 +2808,7 @@
         <f t="shared" si="5"/>
         <v>124487.04578100001</v>
       </c>
-      <c r="O9" s="226"/>
+      <c r="O9" s="216"/>
     </row>
     <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="210" t="s">
@@ -2954,7 +2975,7 @@
       <c r="A14" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="227" t="s">
+      <c r="B14" s="217" t="s">
         <v>125</v>
       </c>
       <c r="C14" s="186" t="s">
@@ -3638,60 +3659,60 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="219"/>
-      <c r="B33" s="219"/>
-      <c r="C33" s="219"/>
-      <c r="D33" s="219"/>
-      <c r="E33" s="219"/>
-      <c r="F33" s="219"/>
-      <c r="G33" s="219"/>
-      <c r="H33" s="219"/>
-      <c r="I33" s="219"/>
-      <c r="J33" s="219"/>
-      <c r="K33" s="219"/>
-      <c r="L33" s="219"/>
+      <c r="A33" s="222"/>
+      <c r="B33" s="222"/>
+      <c r="C33" s="222"/>
+      <c r="D33" s="222"/>
+      <c r="E33" s="222"/>
+      <c r="F33" s="222"/>
+      <c r="G33" s="222"/>
+      <c r="H33" s="222"/>
+      <c r="I33" s="222"/>
+      <c r="J33" s="222"/>
+      <c r="K33" s="222"/>
+      <c r="L33" s="222"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="219"/>
-      <c r="B34" s="219"/>
-      <c r="C34" s="219"/>
-      <c r="D34" s="219"/>
-      <c r="E34" s="219"/>
-      <c r="F34" s="219"/>
-      <c r="G34" s="219"/>
-      <c r="H34" s="219"/>
-      <c r="I34" s="219"/>
-      <c r="J34" s="219"/>
-      <c r="K34" s="219"/>
-      <c r="L34" s="219"/>
+      <c r="A34" s="222"/>
+      <c r="B34" s="222"/>
+      <c r="C34" s="222"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="222"/>
+      <c r="H34" s="222"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="222"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="222"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="219"/>
-      <c r="B35" s="219"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
-      <c r="H35" s="219"/>
-      <c r="I35" s="219"/>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
+      <c r="A35" s="222"/>
+      <c r="B35" s="222"/>
+      <c r="C35" s="222"/>
+      <c r="D35" s="222"/>
+      <c r="E35" s="222"/>
+      <c r="F35" s="222"/>
+      <c r="G35" s="222"/>
+      <c r="H35" s="222"/>
+      <c r="I35" s="222"/>
+      <c r="J35" s="222"/>
+      <c r="K35" s="222"/>
+      <c r="L35" s="222"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="219"/>
-      <c r="B36" s="219"/>
-      <c r="C36" s="219"/>
-      <c r="D36" s="219"/>
-      <c r="E36" s="219"/>
-      <c r="F36" s="219"/>
-      <c r="G36" s="219"/>
-      <c r="H36" s="219"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="219"/>
-      <c r="K36" s="219"/>
-      <c r="L36" s="219"/>
+      <c r="A36" s="222"/>
+      <c r="B36" s="222"/>
+      <c r="C36" s="222"/>
+      <c r="D36" s="222"/>
+      <c r="E36" s="222"/>
+      <c r="F36" s="222"/>
+      <c r="G36" s="222"/>
+      <c r="H36" s="222"/>
+      <c r="I36" s="222"/>
+      <c r="J36" s="222"/>
+      <c r="K36" s="222"/>
+      <c r="L36" s="222"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3731,22 +3752,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="221" t="s">
+      <c r="A1" s="224" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="223"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="226"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3884,11 +3905,11 @@
         <f>C8-J38</f>
         <v>-290631.84495</v>
       </c>
-      <c r="L8" s="225">
+      <c r="L8" s="228">
         <f>C7-J38</f>
         <v>372270.10504999995</v>
       </c>
-      <c r="M8" s="225"/>
+      <c r="M8" s="228"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -5321,18 +5342,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="224"/>
-      <c r="D40" s="222"/>
-      <c r="E40" s="222"/>
-      <c r="F40" s="222"/>
-      <c r="G40" s="222"/>
-      <c r="H40" s="222"/>
-      <c r="I40" s="222"/>
-      <c r="J40" s="222"/>
-      <c r="K40" s="222"/>
-      <c r="L40" s="222"/>
-      <c r="M40" s="222"/>
-      <c r="N40" s="222"/>
+      <c r="C40" s="227"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="225"/>
+      <c r="I40" s="225"/>
+      <c r="J40" s="225"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="225"/>
+      <c r="N40" s="225"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">

--- a/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
+++ b/ROSALES/Julio/expensas rosales Julioxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8DB37-CE23-4574-B4AA-73AB57F19CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672031D-3180-43AE-8015-6618D5E90EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1154,7 +1154,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1496,6 +1496,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1516,12 +1522,7 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2328,7 +2329,7 @@
       <c r="B53" s="158"/>
       <c r="C53" s="205">
         <f>'prorrateo '!F31</f>
-        <v>2194116.7546521635</v>
+        <v>2167012.7546521635</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -2342,7 +2343,7 @@
       <c r="B55" s="157"/>
       <c r="C55" s="166">
         <f>SUM(C49:C53)</f>
-        <v>656638.60545386374</v>
+        <v>629534.60545386374</v>
       </c>
       <c r="D55" s="5"/>
     </row>
@@ -2400,21 +2401,21 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="229" t="s">
+      <c r="A64" s="221" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="230"/>
-      <c r="C64" s="230"/>
+      <c r="B64" s="222"/>
+      <c r="C64" s="222"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="230"/>
-      <c r="B65" s="230"/>
-      <c r="C65" s="230"/>
+      <c r="A65" s="222"/>
+      <c r="B65" s="222"/>
+      <c r="C65" s="222"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="230"/>
-      <c r="B66" s="230"/>
-      <c r="C66" s="230"/>
+      <c r="A66" s="222"/>
+      <c r="B66" s="222"/>
+      <c r="C66" s="222"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
@@ -2465,21 +2466,21 @@
       <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="221">
+      <c r="B1" s="223">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="221"/>
+      <c r="C1" s="223"/>
       <c r="D1" s="141">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="223">
+      <c r="G1" s="225">
         <v>1000000</v>
       </c>
-      <c r="H1" s="223"/>
+      <c r="H1" s="225"/>
     </row>
     <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2619,17 +2620,17 @@
       <c r="E5" s="131">
         <v>328762.85139613436</v>
       </c>
-      <c r="F5" s="208">
-        <f>E5-50400*2-13326</f>
-        <v>214636.85139613436</v>
+      <c r="F5" s="231">
+        <f>E5-162830</f>
+        <v>165932.85139613436</v>
       </c>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
-        <v>114126</v>
+        <v>162830</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
-        <v>4565.04</v>
+        <v>6513.2</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
@@ -2642,7 +2643,7 @@
       <c r="K5" s="56"/>
       <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>241472.783784</v>
+        <v>292124.943784</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -3341,17 +3342,17 @@
       <c r="E23" s="131">
         <v>70449.182442028789</v>
       </c>
-      <c r="F23" s="208">
-        <f>E23-10800*2</f>
-        <v>48849.182442028789</v>
+      <c r="F23" s="231">
+        <f>E23</f>
+        <v>70449.182442028789</v>
       </c>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
@@ -3364,7 +3365,7 @@
       <c r="K23" s="56"/>
       <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>48774.373668</v>
+        <v>26310.373668</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3637,7 +3638,7 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>2194116.7546521635</v>
+        <v>2167012.7546521635</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
@@ -3652,67 +3653,67 @@
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>4091523.4099954218</v>
+        <v>4119711.5699954215</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="222"/>
-      <c r="B33" s="222"/>
-      <c r="C33" s="222"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="222"/>
-      <c r="K33" s="222"/>
-      <c r="L33" s="222"/>
+      <c r="A33" s="224"/>
+      <c r="B33" s="224"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="224"/>
+      <c r="J33" s="224"/>
+      <c r="K33" s="224"/>
+      <c r="L33" s="224"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="222"/>
-      <c r="B34" s="222"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
-      <c r="L34" s="222"/>
+      <c r="A34" s="224"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="222"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="222"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
-      <c r="L35" s="222"/>
+      <c r="A35" s="224"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="222"/>
-      <c r="B36" s="222"/>
-      <c r="C36" s="222"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
-      <c r="G36" s="222"/>
-      <c r="H36" s="222"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="222"/>
-      <c r="K36" s="222"/>
-      <c r="L36" s="222"/>
+      <c r="A36" s="224"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3752,22 +3753,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="226" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="226"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="228"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3905,11 +3906,11 @@
         <f>C8-J38</f>
         <v>-290631.84495</v>
       </c>
-      <c r="L8" s="228">
+      <c r="L8" s="230">
         <f>C7-J38</f>
         <v>372270.10504999995</v>
       </c>
-      <c r="M8" s="228"/>
+      <c r="M8" s="230"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -4123,7 +4124,7 @@
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>262861.23307851999</v>
+        <v>313513.39307852002</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -5046,7 +5047,7 @@
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>52794.890802540001</v>
+        <v>30330.890802540001</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -5342,18 +5343,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="227"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="225"/>
-      <c r="N40" s="225"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="227"/>
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
